--- a/resources/ai-for-your-business/files/aifyb-int-management-pack.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-int-management-pack.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,11 +66,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -160,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,8 +191,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -563,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -608,7 +601,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -695,7 +687,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>One leading number (e.g. new enquiries)</t>
+          <t>One leading number (e.g. new inquiries)</t>
         </is>
       </c>
       <c r="B12" s="14" t="n"/>
@@ -717,7 +709,6 @@
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="11" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -731,10 +722,6 @@
           <t>('cash is tighter BECAUSE...') travels as a possible explanation until a person confirms it.</t>
         </is>
       </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -797,7 +784,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -925,7 +911,6 @@
       <c r="F17" s="16" t="n"/>
       <c r="G17" s="16" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -936,7 +921,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>overdue debt  |  £X now  |  Grace  |  overdue down a fifth by quarter-end  |  (review date)  |  open</t>
+          <t>overdue debt  |  $X now  |  Grace  |  overdue down a fifth by quarter-end  |  (review date)  |  open</t>
         </is>
       </c>
     </row>
@@ -950,7 +935,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>level now  |  —  |  the number that would make us act (e.g. debt over £Y)  |  (review date)  |  open</t>
+          <t>level now  |  —  |  the number that would make us act (e.g. debt over $Y)  |  (review date)  |  open</t>
         </is>
       </c>
     </row>
@@ -961,7 +946,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>

--- a/resources/ai-for-your-business/files/aifyb-int-management-pack.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-int-management-pack.xlsx
@@ -956,7 +956,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
